--- a/fuction_ensemble/redes-ensemble-s/Teste04/content/results/metrics_27_5.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste04/content/results/metrics_27_5.xlsx
@@ -513,1376 +513,1376 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_27_5_7</t>
+          <t>model_27_5_0</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9745662111013995</v>
+        <v>0.9962147832633247</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6756512960705485</v>
+        <v>0.6519667784612034</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9225308886230121</v>
+        <v>0.9999887938713437</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9087271439448968</v>
+        <v>0.9967025677008436</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9456898395363171</v>
+        <v>0.9974732176976794</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1700758634767709</v>
+        <v>0.002247068167739511</v>
       </c>
       <c r="H2" t="n">
-        <v>2.168921276664697</v>
+        <v>0.206607554557779</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1104718392056094</v>
+        <v>3.163405874064486e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2756760341349631</v>
+        <v>0.003043094463471199</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1930739399721617</v>
+        <v>0.001523128937005299</v>
       </c>
       <c r="L2" t="n">
-        <v>1.047712220081053</v>
+        <v>0.01815354409273565</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4124025502791792</v>
+        <v>0.04740325060309167</v>
       </c>
       <c r="N2" t="n">
-        <v>1.008720156193806</v>
+        <v>1.002671917696477</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4299593806355319</v>
+        <v>0.04942130511952168</v>
       </c>
       <c r="P2" t="n">
-        <v>191.5430213714573</v>
+        <v>128.1962578980327</v>
       </c>
       <c r="Q2" t="n">
-        <v>306.1173489090681</v>
+        <v>198.8910557403884</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_27_5_8</t>
+          <t>model_27_5_1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9762646679403139</v>
+        <v>0.9968790191696139</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6754852646514387</v>
+        <v>0.6487956606462162</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9137324336383208</v>
+        <v>0.9999926015039893</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8932706461619636</v>
+        <v>0.9971040243593822</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9373592727458258</v>
+        <v>0.9977814211686423</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1587182747742764</v>
+        <v>0.001852749040269129</v>
       </c>
       <c r="H3" t="n">
-        <v>2.17003152952879</v>
+        <v>0.2084900670779123</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1230185366834811</v>
+        <v>2.088539803304396e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3223600779413983</v>
+        <v>0.002672602994932247</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2226893073124397</v>
+        <v>0.001337345767367776</v>
       </c>
       <c r="L3" t="n">
-        <v>0.960356947314817</v>
+        <v>0.01650987089160759</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3983946219193683</v>
+        <v>0.04304357141628851</v>
       </c>
       <c r="N3" t="n">
-        <v>1.00813782813475</v>
+        <v>1.002203045292037</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4153551057650345</v>
+        <v>0.04487602536395625</v>
       </c>
       <c r="P3" t="n">
-        <v>191.6812490102447</v>
+        <v>128.5821695502728</v>
       </c>
       <c r="Q3" t="n">
-        <v>306.2555765478555</v>
+        <v>199.2769673926284</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_27_5_6</t>
+          <t>model_27_5_2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9721288249561874</v>
+        <v>0.9974178320414826</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6754622490523126</v>
+        <v>0.6458841020601419</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9312699404107742</v>
+        <v>0.9999914683927289</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9244587689729603</v>
+        <v>0.9974344073518733</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9541253682444544</v>
+        <v>0.9980340614145051</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1863746758529356</v>
+        <v>0.001532886444023771</v>
       </c>
       <c r="H4" t="n">
-        <v>2.170185434946123</v>
+        <v>0.2102184940273881</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09800985136623526</v>
+        <v>2.408408593566068e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2281610095627439</v>
+        <v>0.002367703132232371</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1630854304644896</v>
+        <v>0.001185055770412969</v>
       </c>
       <c r="L4" t="n">
-        <v>1.146446020356852</v>
+        <v>0.01503741677699597</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4317113339407892</v>
+        <v>0.03915209373742062</v>
       </c>
       <c r="N4" t="n">
-        <v>1.009555831443593</v>
+        <v>1.001822706794248</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4500901791923089</v>
+        <v>0.04081887942382963</v>
       </c>
       <c r="P4" t="n">
-        <v>191.3599924902368</v>
+        <v>128.9612055123692</v>
       </c>
       <c r="Q4" t="n">
-        <v>305.9343200278477</v>
+        <v>199.6560033547248</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_27_5_9</t>
+          <t>model_27_5_3</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9773969405494877</v>
+        <v>0.9978552206726236</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6750658690659732</v>
+        <v>0.6432182098533188</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9050410810993794</v>
+        <v>0.9999867144857584</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8783019417803798</v>
+        <v>0.997707688190401</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9292574340959778</v>
+        <v>0.9982421425914979</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1511467626230946</v>
+        <v>0.001273233658373426</v>
       </c>
       <c r="H5" t="n">
-        <v>2.172836029739936</v>
+        <v>0.2118010828019053</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1354125048482742</v>
+        <v>3.750400792346215e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3675708146095094</v>
+        <v>0.002115501015176263</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2514915405555338</v>
+        <v>0.001059625707984305</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8820145988609996</v>
+        <v>0.01374571621015376</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3887759799976004</v>
+        <v>0.03568239984044551</v>
       </c>
       <c r="N5" t="n">
-        <v>1.007749620383033</v>
+        <v>1.001513961878148</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4053269783433233</v>
+        <v>0.03720147347440377</v>
       </c>
       <c r="P5" t="n">
-        <v>191.7790079525835</v>
+        <v>129.3323908537201</v>
       </c>
       <c r="Q5" t="n">
-        <v>306.3533354901943</v>
+        <v>200.0271886960757</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_27_5_5</t>
+          <t>model_27_5_4</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9687302963052703</v>
+        <v>0.9982105318620331</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6747832978309878</v>
+        <v>0.640782679038739</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9397516276050588</v>
+        <v>0.9999793826376999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9401723342197588</v>
+        <v>0.997934679186309</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9625016032774129</v>
+        <v>0.9984141860713382</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2091006525904035</v>
+        <v>0.001062305587695695</v>
       </c>
       <c r="H6" t="n">
-        <v>2.174725584889404</v>
+        <v>0.2132469191028929</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08591486838186065</v>
+        <v>5.820126379760717e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1807005318634027</v>
+        <v>0.001906018308561792</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1333077114126819</v>
+        <v>0.0009559189492630542</v>
       </c>
       <c r="L6" t="n">
-        <v>1.258238550230794</v>
+        <v>0.01260075651956796</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4572752481716056</v>
+        <v>0.03259302974096907</v>
       </c>
       <c r="N6" t="n">
-        <v>1.010721041266764</v>
+        <v>1.001263153979741</v>
       </c>
       <c r="O6" t="n">
-        <v>0.476742402176529</v>
+        <v>0.03398058249391489</v>
       </c>
       <c r="P6" t="n">
-        <v>191.1298791032071</v>
+        <v>129.6946273003886</v>
       </c>
       <c r="Q6" t="n">
-        <v>305.704206640818</v>
+        <v>200.3894251427442</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_27_5_10</t>
+          <t>model_27_5_5</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9780978341552204</v>
+        <v>0.9984993483666766</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6744705787087573</v>
+        <v>0.6385616485783217</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8965843381834202</v>
+        <v>0.9999702881029687</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8639702401119818</v>
+        <v>0.9981240293254755</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9214732185036785</v>
+        <v>0.9985570019670846</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1464598838542412</v>
+        <v>0.0008908516343159525</v>
       </c>
       <c r="H7" t="n">
-        <v>2.176816739099699</v>
+        <v>0.2145654187277168</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1474719170063505</v>
+        <v>8.387445163354742e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4108575796907308</v>
+        <v>0.001731273140843637</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2791646161120495</v>
+        <v>0.0008698303996971273</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8116986966569023</v>
+        <v>0.01157364819353249</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3827007758735814</v>
+        <v>0.02984713779101696</v>
       </c>
       <c r="N7" t="n">
-        <v>1.007509314003924</v>
+        <v>1.001059283505875</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3989931402023386</v>
+        <v>0.03111779223887337</v>
       </c>
       <c r="P7" t="n">
-        <v>191.8420074367397</v>
+        <v>130.0466653205561</v>
       </c>
       <c r="Q7" t="n">
-        <v>306.4163349743505</v>
+        <v>200.7414631629117</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_27_5_11</t>
+          <t>model_27_5_6</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9784726959081629</v>
+        <v>0.9987342857138406</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6737586275098251</v>
+        <v>0.6365394462176477</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8884565983828493</v>
+        <v>0.9999600501656508</v>
       </c>
       <c r="E8" t="n">
-        <v>0.850372740192463</v>
+        <v>0.9982825832966196</v>
       </c>
       <c r="F8" t="n">
-        <v>0.914066835602607</v>
+        <v>0.9986759769102245</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1439531815862357</v>
+        <v>0.0007513826762744657</v>
       </c>
       <c r="H8" t="n">
-        <v>2.181577560045192</v>
+        <v>0.2157658854036064</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1590621669575125</v>
+        <v>1.127753790125167e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.451926798010144</v>
+        <v>0.001584948768430276</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3054944872713979</v>
+        <v>0.000798113030730058</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7485422097599183</v>
+        <v>0.01065302573810285</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3794116255285751</v>
+        <v>0.02741136035067333</v>
       </c>
       <c r="N8" t="n">
-        <v>1.007380789974344</v>
+        <v>1.000893445378465</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3955639639176655</v>
+        <v>0.0285783187101399</v>
       </c>
       <c r="P8" t="n">
-        <v>191.8765343202901</v>
+        <v>130.3871909607088</v>
       </c>
       <c r="Q8" t="n">
-        <v>306.4508618579009</v>
+        <v>201.0819888030644</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_27_5_4</t>
+          <t>model_27_5_7</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9640816675448585</v>
+        <v>0.9989255314804184</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6734308018713252</v>
+        <v>0.6347006631520741</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9477676734607601</v>
+        <v>0.9999491734456915</v>
       </c>
       <c r="E9" t="n">
-        <v>0.955474677490085</v>
+        <v>0.9984158626224239</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9706097671047083</v>
+        <v>0.9987754539290122</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2401860545162446</v>
+        <v>0.0006378509278469381</v>
       </c>
       <c r="H9" t="n">
-        <v>2.183769731599339</v>
+        <v>0.2168574664626234</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07448389527405659</v>
+        <v>1.434795417659225e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1344820887461131</v>
+        <v>0.00146194955520785</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1044829920100849</v>
+        <v>0.0007381488914595738</v>
       </c>
       <c r="L9" t="n">
-        <v>1.383358945993903</v>
+        <v>0.00982890249015733</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4900878028641853</v>
+        <v>0.0252557107967077</v>
       </c>
       <c r="N9" t="n">
-        <v>1.012314856841763</v>
+        <v>1.000758448366764</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5109518552537238</v>
+        <v>0.02633089869185222</v>
       </c>
       <c r="P9" t="n">
-        <v>190.852682857645</v>
+        <v>130.714811914667</v>
       </c>
       <c r="Q9" t="n">
-        <v>305.4270103952558</v>
+        <v>201.4096097570226</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_27_5_12</t>
+          <t>model_27_5_8</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9786039559545547</v>
+        <v>0.9990813340670859</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6729750922438755</v>
+        <v>0.6330306167508525</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8807213160428646</v>
+        <v>0.9999380144579055</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8375675386798745</v>
+        <v>0.9985282711416578</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9070758190317965</v>
+        <v>0.9988588889571386</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1430754450516167</v>
+        <v>0.0005453597820798231</v>
       </c>
       <c r="H10" t="n">
-        <v>2.186817063976445</v>
+        <v>0.2178488781486367</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1700927680794794</v>
+        <v>1.749805253734001e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4906029972862819</v>
+        <v>0.001358211339683225</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3303477210348969</v>
+        <v>0.0006878547661673316</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6917868576966036</v>
+        <v>0.009088800058184278</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3782531494272278</v>
+        <v>0.02335293947407528</v>
       </c>
       <c r="N10" t="n">
-        <v>1.007335786529867</v>
+        <v>1.000648470070292</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3943561690903077</v>
+        <v>0.02434712245473569</v>
       </c>
       <c r="P10" t="n">
-        <v>191.8887664001484</v>
+        <v>131.0281296609988</v>
       </c>
       <c r="Q10" t="n">
-        <v>306.4630939377592</v>
+        <v>201.7229275033544</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_27_5_13</t>
+          <t>model_27_5_9</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9785559343252335</v>
+        <v>0.9992083392168092</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6721542071537669</v>
+        <v>0.6315151955151281</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8734196006146566</v>
+        <v>0.9999268554005621</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8255832749557899</v>
+        <v>0.9986233833420188</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9005204021884745</v>
+        <v>0.998929083779231</v>
       </c>
       <c r="G11" t="n">
-        <v>0.143396565908007</v>
+        <v>0.0004699640388672569</v>
       </c>
       <c r="H11" t="n">
-        <v>2.192306326353829</v>
+        <v>0.2187484976569514</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1805050978244894</v>
+        <v>2.064817053364702e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5267996765431315</v>
+        <v>0.001270435341855736</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3536523871838105</v>
+        <v>0.0006455417561946916</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6407757511948438</v>
+        <v>0.008423736185157116</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3786773902783304</v>
+        <v>0.02167865399113277</v>
       </c>
       <c r="N11" t="n">
-        <v>1.007352251088491</v>
+        <v>1.00055881937637</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3947984707527414</v>
+        <v>0.02260155917253558</v>
       </c>
       <c r="P11" t="n">
-        <v>191.8842825974926</v>
+        <v>131.3257087584717</v>
       </c>
       <c r="Q11" t="n">
-        <v>306.4586101351034</v>
+        <v>202.0205066008273</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_27_5_14</t>
+          <t>model_27_5_10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.978378637739414</v>
+        <v>0.9993119706654859</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6713214969300856</v>
+        <v>0.6301414875283453</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8665725592318239</v>
+        <v>0.9999158909838646</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8144242514462121</v>
+        <v>0.9987041561244685</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8944067441589439</v>
+        <v>0.9989883473498732</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1445821489937574</v>
+        <v>0.0004084439342872058</v>
       </c>
       <c r="H12" t="n">
-        <v>2.197874663453865</v>
+        <v>0.2195639900590009</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1902690571785288</v>
+        <v>2.37433429389036e-05</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5605038409453281</v>
+        <v>0.00119589273270652</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3753865900166898</v>
+        <v>0.0006098180378227116</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5949072615011406</v>
+        <v>0.007826252628542805</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3802395941952356</v>
+        <v>0.02020999590022734</v>
       </c>
       <c r="N12" t="n">
-        <v>1.007413038489344</v>
+        <v>1.000485667765539</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3964271809245972</v>
+        <v>0.02107037726615893</v>
       </c>
       <c r="P12" t="n">
-        <v>191.8678148556407</v>
+        <v>131.606311801701</v>
       </c>
       <c r="Q12" t="n">
-        <v>306.4421423932516</v>
+        <v>202.3011096440566</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_27_5_3</t>
+          <t>model_27_5_11</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9577995369400137</v>
+        <v>0.9993965972372054</v>
       </c>
       <c r="C13" t="n">
-        <v>0.671137965492403</v>
+        <v>0.6288968665149202</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9551657531028098</v>
+        <v>0.9999052779589002</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9698450839417697</v>
+        <v>0.9987729515672591</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9781980497677232</v>
+        <v>0.9990385247495231</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2821946907973935</v>
+        <v>0.0003582059456370284</v>
       </c>
       <c r="H13" t="n">
-        <v>2.199101939022732</v>
+        <v>0.2203028508573984</v>
       </c>
       <c r="I13" t="n">
-        <v>0.06393414905753321</v>
+        <v>2.673932009957426e-05</v>
       </c>
       <c r="J13" t="n">
-        <v>0.09107842164582805</v>
+        <v>0.001132403626009319</v>
       </c>
       <c r="K13" t="n">
-        <v>0.077506462777577</v>
+        <v>0.0005795714078219828</v>
       </c>
       <c r="L13" t="n">
-        <v>1.523839641018197</v>
+        <v>0.007289254594796762</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5312200022564977</v>
+        <v>0.01892632942852439</v>
       </c>
       <c r="N13" t="n">
-        <v>1.014468730191995</v>
+        <v>1.000425931361973</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5538351375295578</v>
+        <v>0.01973206245519967</v>
       </c>
       <c r="P13" t="n">
-        <v>190.530316106714</v>
+        <v>131.8688049396475</v>
       </c>
       <c r="Q13" t="n">
-        <v>305.1046436443248</v>
+        <v>202.5636027820031</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>model_27_5_15</t>
+          <t>model_27_5_12</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9781108575337542</v>
+        <v>0.999465778887594</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6704958368916718</v>
+        <v>0.6277702273318122</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8601874651248955</v>
+        <v>0.9998951230092818</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8040795123115723</v>
+        <v>0.9988317452595884</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8887316782578738</v>
+        <v>0.9990811526152935</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1463727964620196</v>
+        <v>0.0003171367294746282</v>
       </c>
       <c r="H14" t="n">
-        <v>2.203395855932553</v>
+        <v>0.2209716725447699</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1993742744316442</v>
+        <v>2.960598603378293e-05</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5917485809705177</v>
+        <v>0.001078144813884436</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3955615871768248</v>
+        <v>0.0005538755907277099</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5536591074625563</v>
+        <v>0.00680653414328777</v>
       </c>
       <c r="M14" t="n">
-        <v>0.382586978949911</v>
+        <v>0.01780833314700251</v>
       </c>
       <c r="N14" t="n">
-        <v>1.00750484884557</v>
+        <v>1.000377097255816</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3988744987080354</v>
+        <v>0.01856647075740205</v>
       </c>
       <c r="P14" t="n">
-        <v>191.8431970224744</v>
+        <v>132.1123551076327</v>
       </c>
       <c r="Q14" t="n">
-        <v>306.4175245600853</v>
+        <v>202.8071529499883</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_27_5_16</t>
+          <t>model_27_5_13</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9777824170998815</v>
+        <v>0.9995223852329196</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6696909104440422</v>
+        <v>0.6267510359040953</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8542613329083658</v>
+        <v>0.999885479279685</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7945240666120353</v>
+        <v>0.998882132874832</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8834840604601251</v>
+        <v>0.9991174663440968</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1485690791556554</v>
+        <v>0.0002835327576225994</v>
       </c>
       <c r="H15" t="n">
-        <v>2.208778402794197</v>
+        <v>0.2215767086030398</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2078250067777251</v>
+        <v>3.232833839919794e-05</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6206093780211767</v>
+        <v>0.00103164370057444</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4142169959443407</v>
+        <v>0.0005319858968272028</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5165585189963156</v>
+        <v>0.006372512337348112</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3854465970217605</v>
+        <v>0.01683843097270644</v>
       </c>
       <c r="N15" t="n">
-        <v>1.007617456994326</v>
+        <v>1.000337139835586</v>
       </c>
       <c r="O15" t="n">
-        <v>0.401855856641429</v>
+        <v>0.01755527783957191</v>
       </c>
       <c r="P15" t="n">
-        <v>191.8134104988049</v>
+        <v>132.3363657886037</v>
       </c>
       <c r="Q15" t="n">
-        <v>306.3877380364157</v>
+        <v>203.0311636309594</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_27_5_17</t>
+          <t>model_27_5_14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9774162633769079</v>
+        <v>0.9995687501528039</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6689162574440206</v>
+        <v>0.6258293430440302</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8487822149747045</v>
+        <v>0.9998763993712398</v>
       </c>
       <c r="E16" t="n">
-        <v>0.785727070604967</v>
+        <v>0.9989254272326784</v>
       </c>
       <c r="F16" t="n">
-        <v>0.878648131376903</v>
+        <v>0.999148481294572</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1510175507871625</v>
+        <v>0.0002560085383190122</v>
       </c>
       <c r="H16" t="n">
-        <v>2.21395851097229</v>
+        <v>0.2221238652998329</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2156382916418109</v>
+        <v>3.489152829217653e-05</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6471793910167775</v>
+        <v>0.0009916887269133343</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4314088413292942</v>
+        <v>0.0005132902741354299</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4831835360635213</v>
+        <v>0.00598223117924335</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3886097667161268</v>
+        <v>0.01600026682024435</v>
       </c>
       <c r="N16" t="n">
-        <v>1.007742995413632</v>
+        <v>1.000304411656844</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4051536890183485</v>
+        <v>0.01668143130390053</v>
       </c>
       <c r="P16" t="n">
-        <v>191.7807184370858</v>
+        <v>132.5405995224645</v>
       </c>
       <c r="Q16" t="n">
-        <v>306.3550459746966</v>
+        <v>203.2353973648202</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_27_5_18</t>
+          <t>model_27_5_15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9770296280644034</v>
+        <v>0.9996067726291641</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6681783473446903</v>
+        <v>0.6249964197924563</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8437343547723906</v>
+        <v>0.9998678968228738</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7776488234993606</v>
+        <v>0.9989627606338246</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8742040286709893</v>
+        <v>0.9991750698603024</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1536029829021714</v>
+        <v>0.0002334367538661511</v>
       </c>
       <c r="H17" t="n">
-        <v>2.218892919204277</v>
+        <v>0.2226183245223781</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2228365980466535</v>
+        <v>3.729173377531754e-05</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6715785302689925</v>
+        <v>0.0009572349289203917</v>
       </c>
       <c r="K17" t="n">
-        <v>0.447207734423073</v>
+        <v>0.000497262849129212</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4531578063566197</v>
+        <v>0.005631368597792881</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3919221643415583</v>
+        <v>0.01527863717306459</v>
       </c>
       <c r="N17" t="n">
-        <v>1.007875556092205</v>
+        <v>1.000277572261767</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4086071022683029</v>
+        <v>0.01592908038866102</v>
       </c>
       <c r="P17" t="n">
-        <v>191.7467680770422</v>
+        <v>132.7251987578637</v>
       </c>
       <c r="Q17" t="n">
-        <v>306.3210956146531</v>
+        <v>203.4199966002193</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_27_5_19</t>
+          <t>model_27_5_16</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9766355592458191</v>
+        <v>0.9996379916121919</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6674811779289975</v>
+        <v>0.6242438613425594</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8390962561208809</v>
+        <v>0.999859975094192</v>
       </c>
       <c r="E18" t="n">
-        <v>0.770249235313782</v>
+        <v>0.998995028013013</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8701304991934894</v>
+        <v>0.999197914584163</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1562381229065647</v>
+        <v>0.0002149038169510064</v>
       </c>
       <c r="H18" t="n">
-        <v>2.223554894297184</v>
+        <v>0.2230650757270693</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2294505797916606</v>
+        <v>3.952797822806823e-05</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6939278815810708</v>
+        <v>0.0009274564000377336</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4616892306863657</v>
+        <v>0.0004834921891329009</v>
       </c>
       <c r="L18" t="n">
-        <v>0.426144062097187</v>
+        <v>0.005315862311419363</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3952696837686452</v>
+        <v>0.01465959811696782</v>
       </c>
       <c r="N18" t="n">
-        <v>1.008010665401433</v>
+        <v>1.00025553533257</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4120971325277214</v>
+        <v>0.01528368755835871</v>
       </c>
       <c r="P18" t="n">
-        <v>191.7127480133055</v>
+        <v>132.8906399859038</v>
       </c>
       <c r="Q18" t="n">
-        <v>306.2870755509164</v>
+        <v>203.5854378282594</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_27_5_2</t>
+          <t>model_27_5_17</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9493514359919655</v>
+        <v>0.9996636607895726</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6674656812573438</v>
+        <v>0.6235643058077081</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9619538042982084</v>
+        <v>0.9998526273618386</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9825749035272161</v>
+        <v>0.999022992813663</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9849671723243657</v>
+        <v>0.9992176009213483</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3386871807369197</v>
+        <v>0.0001996654844070941</v>
       </c>
       <c r="H19" t="n">
-        <v>2.223658520611888</v>
+        <v>0.2234684892478276</v>
       </c>
       <c r="I19" t="n">
-        <v>0.05425431038572581</v>
+        <v>4.160218783256488e-05</v>
       </c>
       <c r="J19" t="n">
-        <v>0.05262990222565314</v>
+        <v>0.0009016485828303823</v>
       </c>
       <c r="K19" t="n">
-        <v>0.05344206762559904</v>
+        <v>0.0004716253853314736</v>
       </c>
       <c r="L19" t="n">
-        <v>1.682395163684825</v>
+        <v>0.005032017041699152</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5819683674710505</v>
+        <v>0.01413030376202487</v>
       </c>
       <c r="N19" t="n">
-        <v>1.017365221945612</v>
+        <v>1.000237415913243</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6067439657148923</v>
+        <v>0.01473186004693547</v>
       </c>
       <c r="P19" t="n">
-        <v>190.1653567366084</v>
+        <v>133.0377343394019</v>
       </c>
       <c r="Q19" t="n">
-        <v>304.7396842742193</v>
+        <v>203.7325321817575</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_27_5_20</t>
+          <t>model_27_5_18</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.976243613020719</v>
+        <v>0.999684794172384</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6668268899049115</v>
+        <v>0.6229508150502951</v>
       </c>
       <c r="D20" t="n">
-        <v>0.834846154124364</v>
+        <v>0.9998458273282098</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7634845507811087</v>
+        <v>0.9990472907791244</v>
       </c>
       <c r="F20" t="n">
-        <v>0.866404386038008</v>
+        <v>0.9992346081919591</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1588590691185559</v>
+        <v>0.0001871197954556371</v>
       </c>
       <c r="H20" t="n">
-        <v>2.227930121326966</v>
+        <v>0.2238326838628488</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2355112738672883</v>
+        <v>4.352178620453947e-05</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7143596012044344</v>
+        <v>0.0008792247701602605</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4749356534840293</v>
+        <v>0.000461373506496079</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4018382873790513</v>
+        <v>0.00477674924960988</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3985712848645219</v>
+        <v>0.01367917378556312</v>
       </c>
       <c r="N20" t="n">
-        <v>1.008145046964325</v>
+        <v>1.000222498231258</v>
       </c>
       <c r="O20" t="n">
-        <v>0.415539289617506</v>
+        <v>0.01426152453340795</v>
       </c>
       <c r="P20" t="n">
-        <v>191.6794756551083</v>
+        <v>133.1675230576152</v>
       </c>
       <c r="Q20" t="n">
-        <v>306.2538031927191</v>
+        <v>203.8623208999708</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_27_5_21</t>
+          <t>model_27_5_19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9758607318508075</v>
+        <v>0.999702226564207</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6662162567279883</v>
+        <v>0.6223971441820537</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8309596734258768</v>
+        <v>0.9998395673464423</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7573116988486877</v>
+        <v>0.9990684650360998</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8630027368663409</v>
+        <v>0.9992493522727869</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1614193972647597</v>
+        <v>0.0001767711746293859</v>
       </c>
       <c r="H21" t="n">
-        <v>2.232013428192759</v>
+        <v>0.224161366807573</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2410534398114625</v>
+        <v>4.528893199611263e-05</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7330037788228583</v>
+        <v>0.0008596837278204763</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4870285989360313</v>
+        <v>0.0004524858646371843</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3799686838123054</v>
+        <v>0.004547041748078178</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4017703289999894</v>
+        <v>0.01329553213035815</v>
       </c>
       <c r="N21" t="n">
-        <v>1.008276320508295</v>
+        <v>1.000210193013501</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4188745236847547</v>
+        <v>0.0138615504586932</v>
       </c>
       <c r="P21" t="n">
-        <v>191.6474986980985</v>
+        <v>133.2813089209593</v>
       </c>
       <c r="Q21" t="n">
-        <v>306.2218262357094</v>
+        <v>203.9761067633149</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_27_5_22</t>
+          <t>model_27_5_20</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9754917297374872</v>
+        <v>0.9997166153462337</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6656490387871237</v>
+        <v>0.6218976562857057</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8274116493773146</v>
+        <v>0.9998338206001629</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7516872270052495</v>
+        <v>0.9990869159445958</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8599018549523275</v>
+        <v>0.9992621299867137</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1638869160956307</v>
+        <v>0.000168229372055324</v>
       </c>
       <c r="H22" t="n">
-        <v>2.23580641717512</v>
+        <v>0.2244578843995989</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2461129627003082</v>
+        <v>4.691119526781475e-05</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7499916562589133</v>
+        <v>0.0008426559764078863</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4980523094796107</v>
+        <v>0.0004447835367347065</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3602884198800644</v>
+        <v>0.004340554086332995</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4048294901506444</v>
+        <v>0.01297032659786653</v>
       </c>
       <c r="N22" t="n">
-        <v>1.008402835518576</v>
+        <v>1.000200036226188</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4220639196589297</v>
+        <v>0.01352250025341516</v>
       </c>
       <c r="P22" t="n">
-        <v>191.617157249999</v>
+        <v>133.3803643997918</v>
       </c>
       <c r="Q22" t="n">
-        <v>306.1914847876098</v>
+        <v>204.0751622421475</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_27_5_23</t>
+          <t>model_27_5_21</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9751398675268378</v>
+        <v>0.9997285310570129</v>
       </c>
       <c r="C23" t="n">
-        <v>0.66512418110865</v>
+        <v>0.621447047607333</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8241780883846745</v>
+        <v>0.9998285483862315</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7465692603328435</v>
+        <v>0.9991031011358604</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8570792091005917</v>
+        <v>0.9992732850343231</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1662398203184206</v>
+        <v>0.000161155691404897</v>
       </c>
       <c r="H23" t="n">
-        <v>2.23931614288782</v>
+        <v>0.2247253851763623</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2507240576734018</v>
+        <v>4.839950162510897e-05</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7654497104500959</v>
+        <v>0.0008277191827274784</v>
       </c>
       <c r="K23" t="n">
-        <v>0.508086884061749</v>
+        <v>0.0004380593421762937</v>
       </c>
       <c r="L23" t="n">
-        <v>0.342582438387609</v>
+        <v>0.004154741823798586</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4077251774399278</v>
+        <v>0.01269471115878171</v>
       </c>
       <c r="N23" t="n">
-        <v>1.008523473990798</v>
+        <v>1.000191625136226</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4250828823510168</v>
+        <v>0.01323515129448589</v>
       </c>
       <c r="P23" t="n">
-        <v>191.5886476649765</v>
+        <v>133.4662792657799</v>
       </c>
       <c r="Q23" t="n">
-        <v>306.1629752025873</v>
+        <v>204.1610771081355</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_27_5_24</t>
+          <t>model_27_5_22</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9748072787726029</v>
+        <v>0.9997384023292412</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6646401928466583</v>
+        <v>0.6210407710533331</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8212357641953649</v>
+        <v>0.9998237147233437</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7419185773094672</v>
+        <v>0.999117264178188</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8545134862305523</v>
+        <v>0.9992829950666888</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1684638428494195</v>
+        <v>0.0001552956777934525</v>
       </c>
       <c r="H24" t="n">
-        <v>2.242552574624319</v>
+        <v>0.2249665684890499</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2549198456326883</v>
+        <v>4.976400831972114e-05</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7794964041476085</v>
+        <v>0.0008146485654158355</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5172080912017356</v>
+        <v>0.0004322061939799027</v>
       </c>
       <c r="L24" t="n">
-        <v>0.3266468941992021</v>
+        <v>0.003987526419450583</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4104434709547949</v>
+        <v>0.01246176864628181</v>
       </c>
       <c r="N24" t="n">
-        <v>1.008637504420822</v>
+        <v>1.000184657179359</v>
       </c>
       <c r="O24" t="n">
-        <v>0.4279168992484552</v>
+        <v>0.01299229193697139</v>
       </c>
       <c r="P24" t="n">
-        <v>191.5620682694237</v>
+        <v>133.5403593190667</v>
       </c>
       <c r="Q24" t="n">
-        <v>306.1363958070345</v>
+        <v>204.2351571614224</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_27_5_1</t>
+          <t>model_27_5_23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9379185441786679</v>
+        <v>0.9997466077549686</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6615182943140194</v>
+        <v>0.6206743473851897</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9681856954974302</v>
+        <v>0.9998193194619686</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9925886369741002</v>
+        <v>0.9991297299586074</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9904708890007391</v>
+        <v>0.9992915082035024</v>
       </c>
       <c r="G25" t="n">
-        <v>0.415138980936067</v>
+        <v>0.0001504245826256824</v>
       </c>
       <c r="H25" t="n">
-        <v>2.263428724487096</v>
+        <v>0.2251840934071381</v>
       </c>
       <c r="I25" t="n">
-        <v>0.04536756223190901</v>
+        <v>5.100475756318995e-05</v>
       </c>
       <c r="J25" t="n">
-        <v>0.02238491545921488</v>
+        <v>0.0008031442966590732</v>
       </c>
       <c r="K25" t="n">
-        <v>0.03387622112237437</v>
+        <v>0.0004270745271111316</v>
       </c>
       <c r="L25" t="n">
-        <v>1.863029187956228</v>
+        <v>0.003837070127870053</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6443127974331</v>
+        <v>0.01226476997850683</v>
       </c>
       <c r="N25" t="n">
-        <v>1.021285070567314</v>
+        <v>1.00017886511414</v>
       </c>
       <c r="O25" t="n">
-        <v>0.6717425271311878</v>
+        <v>0.01278690662806576</v>
       </c>
       <c r="P25" t="n">
-        <v>189.758283841988</v>
+        <v>133.6040974229914</v>
       </c>
       <c r="Q25" t="n">
-        <v>304.3326113795989</v>
+        <v>204.298895265347</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>model_27_5_0</t>
+          <t>model_27_5_24</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9219398439327996</v>
+        <v>0.9997534358512312</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6507839050693047</v>
+        <v>0.6203441575445278</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9716845544796281</v>
+        <v>0.9998153041993088</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9980971590466494</v>
+        <v>0.9991406980054667</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9935126448743276</v>
+        <v>0.9992989635568089</v>
       </c>
       <c r="G26" t="n">
-        <v>0.5219886230553378</v>
+        <v>0.0001463711297257787</v>
       </c>
       <c r="H26" t="n">
-        <v>2.335209634793821</v>
+        <v>0.2253801083600135</v>
       </c>
       <c r="I26" t="n">
-        <v>0.04037814929023321</v>
+        <v>5.213823602602831e-05</v>
       </c>
       <c r="J26" t="n">
-        <v>0.005747246994140132</v>
+        <v>0.0007930222381466933</v>
       </c>
       <c r="K26" t="n">
-        <v>0.02306270508903658</v>
+        <v>0.0004225804856789294</v>
       </c>
       <c r="L26" t="n">
-        <v>2.077882426693196</v>
+        <v>0.003701716652837954</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7224878013193979</v>
+        <v>0.01209839368369945</v>
       </c>
       <c r="N26" t="n">
-        <v>1.026763482080183</v>
+        <v>1.000174045281484</v>
       </c>
       <c r="O26" t="n">
-        <v>0.7532456027774924</v>
+        <v>0.01261344734994202</v>
       </c>
       <c r="P26" t="n">
-        <v>189.3002189725003</v>
+        <v>133.6587303544209</v>
       </c>
       <c r="Q26" t="n">
-        <v>303.8745465101111</v>
+        <v>204.3535281967765</v>
       </c>
     </row>
   </sheetData>
